--- a/myapp/cert_templates/Acknowledgement-Receipt-Form.xlsx
+++ b/myapp/cert_templates/Acknowledgement-Receipt-Form.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\thesis_osa\myproject\myapp\cert_templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\thesis_osa\myapp\cert_templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8575B8F-66CD-4BAB-8D9D-48FDEC36B486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67A7272B-46E1-4647-A27F-516C30540777}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -86,9 +86,6 @@
     <t>student_name</t>
   </si>
   <si>
-    <t>Lord Jaisson Riberal</t>
-  </si>
-  <si>
     <t>student_id</t>
   </si>
   <si>
@@ -192,6 +189,9 @@
   </si>
   <si>
     <t>signature over printed name/date</t>
+  </si>
+  <si>
+    <t>LORD JAISSON RIBERAL</t>
   </si>
 </sst>
 </file>
@@ -204,7 +204,7 @@
     <numFmt numFmtId="166" formatCode="hh:mm:ss"/>
     <numFmt numFmtId="167" formatCode="m/d/yyyy\ h:mm:ss"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -363,6 +363,13 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -411,24 +418,6 @@
   </cellStyleXfs>
   <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="166" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -446,14 +435,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -465,13 +448,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -480,31 +457,61 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -831,83 +838,83 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="7" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" s="13" t="s">
+      <c r="B3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="13" t="s">
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="7" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" s="13" t="s">
+      <c r="B4" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="13" t="s">
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" s="13" t="s">
+      <c r="B5" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="13" t="s">
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="7" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" s="13" t="s">
+      <c r="B6" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="13" t="s">
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" s="7" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" s="13" t="s">
+      <c r="B7" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="13" t="s">
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" s="7" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8" s="13" t="s">
+      <c r="B8" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="13" t="s">
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" s="7" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" s="13" t="s">
+      <c r="B9" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="13" t="s">
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" s="7" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10" s="13" t="s">
+      <c r="B10" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -944,295 +951,295 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
-      <c r="L1" s="12"/>
-      <c r="M1" s="15" t="s">
+      <c r="N1" s="8"/>
+      <c r="O1" s="6"/>
+    </row>
+    <row r="2" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="N1" s="15"/>
-      <c r="O1" s="14"/>
-    </row>
-    <row r="2" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="11" t="s">
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="33"/>
+      <c r="L2" s="33"/>
+      <c r="M2" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="11"/>
-      <c r="L2" s="11"/>
-      <c r="M2" s="15" t="s">
+      <c r="N2" s="8"/>
+      <c r="O2" s="5"/>
+    </row>
+    <row r="3" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F3" s="9"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="N2" s="15"/>
-      <c r="O2" s="16"/>
-    </row>
-    <row r="3" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F3" s="17"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="K3" s="16"/>
-      <c r="L3" s="17"/>
-      <c r="M3" s="19" t="s">
+      <c r="N3" s="11"/>
+      <c r="O3" s="12"/>
+    </row>
+    <row r="4" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4"/>
+      <c r="B4" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="N3" s="19"/>
-      <c r="O3" s="20"/>
-    </row>
-    <row r="4" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="21"/>
-      <c r="B4" s="10" t="s">
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="34"/>
+      <c r="J4" s="34"/>
+      <c r="K4" s="34"/>
+      <c r="L4" s="34"/>
+      <c r="M4" s="34"/>
+      <c r="N4" s="34"/>
+      <c r="O4" s="13"/>
+    </row>
+    <row r="5" spans="1:15" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A5" s="3"/>
+      <c r="B5" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
-      <c r="N4" s="10"/>
-      <c r="O4" s="22"/>
-    </row>
-    <row r="5" spans="1:15" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A5" s="23"/>
-      <c r="B5" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9"/>
-      <c r="N5" s="9"/>
-      <c r="O5" s="9"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
+      <c r="E5" s="35"/>
+      <c r="F5" s="35"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="35"/>
+      <c r="I5" s="35"/>
+      <c r="J5" s="35"/>
+      <c r="K5" s="35"/>
+      <c r="L5" s="35"/>
+      <c r="M5" s="35"/>
+      <c r="N5" s="35"/>
+      <c r="O5" s="35"/>
     </row>
     <row r="6" spans="1:15" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E6" s="24" t="str">
+      <c r="E6" s="14" t="str">
         <f t="array" ref="E6">IFERROR(INDEX(#REF!, MATCH($B$7,#REF!,0)),"Select a student from the list in cell B4")</f>
         <v>Select a student from the list in cell B4</v>
       </c>
-      <c r="K6" s="22"/>
-      <c r="L6" s="25"/>
-      <c r="M6" s="22"/>
-      <c r="N6" s="22"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="13"/>
+      <c r="N6" s="13"/>
     </row>
     <row r="7" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" s="28"/>
-      <c r="E7" s="8" t="str">
+      <c r="D7" s="2"/>
+      <c r="E7" s="36" t="str">
         <f>UPPER(student_name)</f>
         <v>LORD JAISSON RIBERAL</v>
       </c>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="M7" s="28"/>
-      <c r="N7" s="28"/>
-      <c r="O7" s="28"/>
+      <c r="F7" s="36"/>
+      <c r="G7" s="36"/>
+      <c r="H7" s="36"/>
+      <c r="I7" s="36"/>
+      <c r="J7" s="36"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="C8" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" s="22"/>
-      <c r="E8" s="7" t="str">
+      <c r="C8" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="13"/>
+      <c r="E8" s="25" t="str">
         <f>student_id</f>
         <v>TUPC-22-0374</v>
       </c>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="J8" s="27" t="s">
-        <v>30</v>
-      </c>
-      <c r="K8" s="30"/>
-      <c r="L8" s="7" t="str">
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
+      <c r="J8" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="K8" s="18"/>
+      <c r="L8" s="25" t="str">
         <f>proof</f>
         <v>Affidavit of Loss</v>
       </c>
-      <c r="M8" s="7"/>
-      <c r="N8" s="7"/>
+      <c r="M8" s="25"/>
+      <c r="N8" s="25"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="C9" s="27" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" s="22"/>
-      <c r="E9" s="7" t="str">
+      <c r="C9" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="13"/>
+      <c r="E9" s="25" t="str">
         <f>year_level</f>
         <v>1st Year</v>
       </c>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="J9" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="K9" s="31"/>
-      <c r="L9" s="6" t="e">
+      <c r="F9" s="25"/>
+      <c r="G9" s="25"/>
+      <c r="J9" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="K9" s="19"/>
+      <c r="L9" s="30" t="e">
         <f>TEXT(DATEVALUE(timestamp), "MMMM D, YYYY")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="M9" s="6"/>
-      <c r="N9" s="32"/>
+      <c r="M9" s="30"/>
+      <c r="N9" s="20"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="C10" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10" s="22"/>
-      <c r="E10" s="29" t="str">
+      <c r="C10" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" s="13"/>
+      <c r="E10" s="1" t="str">
         <f>program</f>
         <v>BET-COET</v>
       </c>
-      <c r="F10" s="29"/>
-      <c r="G10" s="33"/>
-      <c r="J10" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="K10" s="31"/>
-      <c r="L10" s="5" t="str">
+      <c r="F10" s="1"/>
+      <c r="G10" s="21"/>
+      <c r="J10" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="K10" s="19"/>
+      <c r="L10" s="31" t="str">
         <f>reason</f>
         <v>Claim of Credentials</v>
       </c>
-      <c r="M10" s="5"/>
-      <c r="N10" s="5"/>
+      <c r="M10" s="31"/>
+      <c r="N10" s="31"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="C11" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="D11" s="22"/>
-      <c r="E11" s="7" t="str">
+      <c r="C11" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" s="13"/>
+      <c r="E11" s="25" t="str">
         <f>years_of_stay</f>
         <v>2022-2025</v>
       </c>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="25"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="C12" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="E12" s="4" t="str">
+      <c r="C12" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" s="26" t="str">
         <f>timestamp</f>
         <v>10/08/2025 8:57:32PM</v>
       </c>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="I12" s="34" t="s">
-        <v>37</v>
+      <c r="F12" s="26"/>
+      <c r="G12" s="26"/>
+      <c r="I12" s="22" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="14" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A14" s="35"/>
-      <c r="B14" s="3" t="str">
+      <c r="A14" s="23"/>
+      <c r="B14" s="27" t="str">
         <f>IF(L8="Affidavit of Loss","NOTE: The previously issued TUPC ID is hereby declared invalid, as per the submitted Affidavit of Loss.","The returned TUPC ID has been physically invalidated with a punched hole in the QR code and is no longer considered valid.")</f>
         <v>NOTE: The previously issued TUPC ID is hereby declared invalid, as per the submitted Affidavit of Loss.</v>
       </c>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="35"/>
-      <c r="J14" s="35"/>
-      <c r="K14" s="35"/>
-      <c r="L14" s="35"/>
-      <c r="M14" s="35"/>
-      <c r="N14" s="35"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="27"/>
+      <c r="G14" s="23"/>
+      <c r="H14" s="23"/>
+      <c r="I14" s="23"/>
+      <c r="J14" s="23"/>
+      <c r="K14" s="23"/>
+      <c r="L14" s="23"/>
+      <c r="M14" s="23"/>
+      <c r="N14" s="23"/>
     </row>
     <row r="15" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="I15" s="2" t="str">
+      <c r="B15" s="27"/>
+      <c r="C15" s="27"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="27"/>
+      <c r="I15" s="28" t="str">
         <f>UPPER(osa_head)</f>
         <v>BEVERLY M. DE VEGA</v>
       </c>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
+      <c r="J15" s="28"/>
+      <c r="K15" s="28"/>
+      <c r="L15" s="28"/>
+      <c r="M15" s="28"/>
     </row>
     <row r="16" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="I16" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
+      <c r="B16" s="27"/>
+      <c r="C16" s="27"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
+      <c r="I16" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="J16" s="29"/>
+      <c r="K16" s="29"/>
+      <c r="L16" s="29"/>
+      <c r="M16" s="29"/>
     </row>
     <row r="17" spans="7:12" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G17" s="36"/>
-      <c r="L17" s="34"/>
+      <c r="G17" s="24"/>
+      <c r="L17" s="22"/>
     </row>
     <row r="18" spans="7:12" ht="10.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G18" s="36"/>
-      <c r="L18" s="34"/>
+      <c r="G18" s="24"/>
+      <c r="L18" s="22"/>
     </row>
     <row r="19" spans="7:12" ht="10.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="B4:N4"/>
+    <mergeCell ref="B5:O5"/>
+    <mergeCell ref="E7:J7"/>
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="L10:N10"/>
     <mergeCell ref="E11:G11"/>
     <mergeCell ref="E12:G12"/>
     <mergeCell ref="B14:F16"/>
     <mergeCell ref="I15:M15"/>
     <mergeCell ref="I16:M16"/>
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="B4:N4"/>
-    <mergeCell ref="B5:O5"/>
-    <mergeCell ref="E7:J7"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" sqref="B7" xr:uid="{00000000-0002-0000-0100-000000000000}">
